--- a/data/employees/EMP030/AST-EMP030-06.xlsx
+++ b/data/employees/EMP030/AST-EMP030-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Skyler Chen (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Skyler Chen | Role: Specialist | Location: Fremont | Date: 2025-02-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp030 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>94</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp030 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>93</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP030</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp030 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>72</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP030</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp030 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>71</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>95</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>96</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>93</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>67</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>73</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>63</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>69</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>75</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>61</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>82</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>82</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>83</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp030 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>82</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP030</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP030 contributes to ast emp030 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>